--- a/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_aae.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_gemini-1.5-flash/phi-4/metrics_default_vs_aae.xlsx
@@ -420,7 +420,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.9890109890109891</v>
+        <v>0.9789473684210527</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -429,16 +429,16 @@
         <v>0.7535211267605634</v>
       </c>
       <c r="D2">
-        <v>0.28</v>
+        <v>0.2734375</v>
       </c>
       <c r="E2">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
